--- a/output/pdf_financials_xlsx/RUP.xlsx
+++ b/output/pdf_financials_xlsx/RUP.xlsx
@@ -5933,16 +5933,16 @@
         <v>1.130779</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.646469</v>
+        <v>0.5604</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.646469</v>
+        <v>0.4935</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.4935</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.3185</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.095612</v>
@@ -17402,7 +17402,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -17812,7 +17816,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -19127,7 +19135,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RUP.xlsx
+++ b/output/pdf_financials_xlsx/RUP.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006891</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.328995</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.294369</v>
       </c>
     </row>
     <row r="13">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.113262</v>
+        <v>-0.120153</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.624509</v>
@@ -2078,10 +2078,10 @@
         <v>-13.099969</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.496833</v>
+        <v>-10.825828</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-9.448071000000001</v>
+        <v>-9.74244</v>
       </c>
     </row>
     <row r="28">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.113262</v>
+        <v>-0.120153</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.624509</v>
@@ -2194,10 +2194,10 @@
         <v>-12.88703</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.446773</v>
+        <v>-10.775768</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.448071000000001</v>
+        <v>-9.74244</v>
       </c>
     </row>
     <row r="30">
@@ -2456,25 +2456,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000888</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001105</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.424399</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.319199</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.048336</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.012651</v>
@@ -2572,25 +2572,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.00084</v>
+        <v>0.001728</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.00072</v>
+        <v>0.000965</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.00072</v>
+        <v>0.001825</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.0003</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.00018</v>
+        <v>0.424579</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.00012</v>
+        <v>0.319319</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>6e-05</v>
+        <v>0.048396</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.012735</v>
@@ -3268,25 +3268,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000888</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000245</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001105</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.424399</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.319199</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.048336</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -50467,7 +50467,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -50570,7 +50570,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -52285,7 +52285,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -54661,7 +54661,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -55249,7 +55249,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -55942,7 +55942,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -56942,7 +56942,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -61528,7 +61528,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" s="5" t="n">

--- a/output/pdf_financials_xlsx/RUP.xlsx
+++ b/output/pdf_financials_xlsx/RUP.xlsx
@@ -1343,7 +1343,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.618718</v>
+        <v>-0.618718</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -3802,10 +3802,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>3.17686</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>3.291841</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>0</v>
@@ -3860,10 +3860,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.032543</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.041894</v>
       </c>
       <c r="P57" s="3" t="n">
         <v>0</v>
@@ -6974,16 +6974,16 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.722912</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.864588</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.454833</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.114277</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-0.36951</v>
       </c>
       <c r="Q114" s="3" t="n">
         <v>0</v>
@@ -29637,7 +29637,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -34294,7 +34298,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -36298,7 +36306,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -57538,7 +57550,11 @@
           <t>Deferred income tax recovery (note 21)</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
